--- a/Mod_Korean/Lang/KR/Game/Block.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Block.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="547">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.237 Patch 1</t>
+    <t xml:space="preserve">EA 23.247</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
@@ -1263,6 +1263,27 @@
   </si>
   <si>
     <t xml:space="preserve">201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wire mesh fence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金網のフェンス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stone fence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">石のフェンス</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 11.1</t>
@@ -1740,7 +1761,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -1752,10 +1773,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C4" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1771,10 +1792,10 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C5" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -1790,10 +1811,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C6" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -1809,10 +1830,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C7" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -1828,10 +1849,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C8" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
@@ -1847,10 +1868,10 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C9" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -1866,10 +1887,10 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C10" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -1885,10 +1906,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C11" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -1904,10 +1925,10 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C12" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
@@ -1923,10 +1944,10 @@
         <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C13" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
@@ -1942,10 +1963,10 @@
         <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C14" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
@@ -1961,10 +1982,10 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C15" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="D15" t="s">
         <v>44</v>
@@ -1980,10 +2001,10 @@
         <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C16" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="D16" t="s">
         <v>47</v>
@@ -1992,7 +2013,7 @@
         <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="G16"/>
       <c r="H16" t="s">
@@ -2004,10 +2025,10 @@
         <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C17" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="D17" t="s">
         <v>44</v>
@@ -2023,10 +2044,10 @@
         <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C18" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="D18" t="s">
         <v>52</v>
@@ -2042,10 +2063,10 @@
         <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C19" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D19" t="s">
         <v>35</v>
@@ -2061,10 +2082,10 @@
         <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C20" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="D20" t="s">
         <v>56</v>
@@ -2080,10 +2101,10 @@
         <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C21" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="D21" t="s">
         <v>59</v>
@@ -2099,10 +2120,10 @@
         <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C22" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D22" t="s">
         <v>35</v>
@@ -2118,10 +2139,10 @@
         <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C23" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D23" t="s">
         <v>35</v>
@@ -2137,10 +2158,10 @@
         <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C24" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D24" t="s">
         <v>35</v>
@@ -2156,10 +2177,10 @@
         <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C25" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="D25" t="s">
         <v>65</v>
@@ -2175,10 +2196,10 @@
         <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C26" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="D26" t="s">
         <v>52</v>
@@ -2194,10 +2215,10 @@
         <v>68</v>
       </c>
       <c r="B27" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C27" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="D27" t="s">
         <v>69</v>
@@ -2213,10 +2234,10 @@
         <v>71</v>
       </c>
       <c r="B28" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C28" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="D28" t="s">
         <v>72</v>
@@ -2232,10 +2253,10 @@
         <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C29" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="D29" t="s">
         <v>75</v>
@@ -2251,10 +2272,10 @@
         <v>77</v>
       </c>
       <c r="B30" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C30" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
@@ -2270,10 +2291,10 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C31" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="D31" t="s">
         <v>47</v>
@@ -2282,7 +2303,7 @@
         <v>48</v>
       </c>
       <c r="F31" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="G31"/>
       <c r="H31" t="s">
@@ -2294,10 +2315,10 @@
         <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C32" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="D32" t="s">
         <v>80</v>
@@ -2313,10 +2334,10 @@
         <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C33" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="D33" t="s">
         <v>83</v>
@@ -2332,10 +2353,10 @@
         <v>85</v>
       </c>
       <c r="B34" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C34" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="D34" t="s">
         <v>83</v>
@@ -2351,10 +2372,10 @@
         <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C35" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="D35" t="s">
         <v>83</v>
@@ -2370,10 +2391,10 @@
         <v>87</v>
       </c>
       <c r="B36" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C36" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="D36" t="s">
         <v>88</v>
@@ -2389,10 +2410,10 @@
         <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C37" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="D37" t="s">
         <v>91</v>
@@ -2408,10 +2429,10 @@
         <v>93</v>
       </c>
       <c r="B38" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C38" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="D38" t="s">
         <v>94</v>
@@ -2427,10 +2448,10 @@
         <v>96</v>
       </c>
       <c r="B39" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C39" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="D39" t="s">
         <v>97</v>
@@ -2446,10 +2467,10 @@
         <v>99</v>
       </c>
       <c r="B40" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C40" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="D40" t="s">
         <v>29</v>
@@ -2465,10 +2486,10 @@
         <v>100</v>
       </c>
       <c r="B41" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C41" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="D41" t="s">
         <v>29</v>
@@ -2484,10 +2505,10 @@
         <v>101</v>
       </c>
       <c r="B42" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C42" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="D42" t="s">
         <v>29</v>
@@ -2503,10 +2524,10 @@
         <v>102</v>
       </c>
       <c r="B43" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C43" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="D43" t="s">
         <v>29</v>
@@ -2522,10 +2543,10 @@
         <v>103</v>
       </c>
       <c r="B44" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C44" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="D44" t="s">
         <v>29</v>
@@ -2541,10 +2562,10 @@
         <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C45" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
@@ -2560,10 +2581,10 @@
         <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C46" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="D46" t="s">
         <v>75</v>
@@ -2579,10 +2600,10 @@
         <v>106</v>
       </c>
       <c r="B47" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C47" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="D47" t="s">
         <v>14</v>
@@ -2598,10 +2619,10 @@
         <v>107</v>
       </c>
       <c r="B48" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C48" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="D48" t="s">
         <v>108</v>
@@ -2617,10 +2638,10 @@
         <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C49" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="D49" t="s">
         <v>111</v>
@@ -2636,10 +2657,10 @@
         <v>113</v>
       </c>
       <c r="B50" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C50" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="D50" t="s">
         <v>114</v>
@@ -2655,10 +2676,10 @@
         <v>116</v>
       </c>
       <c r="B51" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C51" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="D51" t="s">
         <v>117</v>
@@ -2674,10 +2695,10 @@
         <v>119</v>
       </c>
       <c r="B52" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C52" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="D52" t="s">
         <v>120</v>
@@ -2693,10 +2714,10 @@
         <v>122</v>
       </c>
       <c r="B53" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C53" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="D53" t="s">
         <v>123</v>
@@ -2712,10 +2733,10 @@
         <v>125</v>
       </c>
       <c r="B54" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C54" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="D54" t="s">
         <v>126</v>
@@ -2731,10 +2752,10 @@
         <v>128</v>
       </c>
       <c r="B55" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C55" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="D55" t="s">
         <v>129</v>
@@ -2750,10 +2771,10 @@
         <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C56" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="D56" t="s">
         <v>132</v>
@@ -2769,10 +2790,10 @@
         <v>134</v>
       </c>
       <c r="B57" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C57" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="D57" t="s">
         <v>135</v>
@@ -2788,10 +2809,10 @@
         <v>137</v>
       </c>
       <c r="B58" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C58" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="D58" t="s">
         <v>117</v>
@@ -2807,10 +2828,10 @@
         <v>138</v>
       </c>
       <c r="B59" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C59" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="D59" t="s">
         <v>139</v>
@@ -2826,10 +2847,10 @@
         <v>141</v>
       </c>
       <c r="B60" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C60" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="D60" t="s">
         <v>142</v>
@@ -2845,10 +2866,10 @@
         <v>144</v>
       </c>
       <c r="B61" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C61" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="D61" t="s">
         <v>142</v>
@@ -2864,10 +2885,10 @@
         <v>145</v>
       </c>
       <c r="B62" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C62" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="D62" t="s">
         <v>142</v>
@@ -2883,10 +2904,10 @@
         <v>146</v>
       </c>
       <c r="B63" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C63" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="D63" t="s">
         <v>147</v>
@@ -2902,10 +2923,10 @@
         <v>149</v>
       </c>
       <c r="B64" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C64" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="D64" t="s">
         <v>150</v>
@@ -2921,10 +2942,10 @@
         <v>152</v>
       </c>
       <c r="B65" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C65" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="D65" t="s">
         <v>150</v>
@@ -2940,10 +2961,10 @@
         <v>153</v>
       </c>
       <c r="B66" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C66" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="D66" t="s">
         <v>150</v>
@@ -2959,10 +2980,10 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C67" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="D67" t="s">
         <v>120</v>
@@ -2978,10 +2999,10 @@
         <v>155</v>
       </c>
       <c r="B68" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C68" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="D68" t="s">
         <v>14</v>
@@ -2997,10 +3018,10 @@
         <v>156</v>
       </c>
       <c r="B69" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C69" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="D69" t="s">
         <v>14</v>
@@ -3016,10 +3037,10 @@
         <v>157</v>
       </c>
       <c r="B70" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C70" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="D70" t="s">
         <v>158</v>
@@ -3035,10 +3056,10 @@
         <v>160</v>
       </c>
       <c r="B71" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C71" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="D71" t="s">
         <v>161</v>
@@ -3054,10 +3075,10 @@
         <v>163</v>
       </c>
       <c r="B72" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C72" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="D72" t="s">
         <v>158</v>
@@ -3073,10 +3094,10 @@
         <v>164</v>
       </c>
       <c r="B73" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C73" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="D73" t="s">
         <v>165</v>
@@ -3092,10 +3113,10 @@
         <v>167</v>
       </c>
       <c r="B74" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C74" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="D74" t="s">
         <v>168</v>
@@ -3111,10 +3132,10 @@
         <v>170</v>
       </c>
       <c r="B75" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C75" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="D75" t="s">
         <v>168</v>
@@ -3130,10 +3151,10 @@
         <v>171</v>
       </c>
       <c r="B76" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C76" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="D76" t="s">
         <v>158</v>
@@ -3149,10 +3170,10 @@
         <v>172</v>
       </c>
       <c r="B77" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C77" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="D77" t="s">
         <v>168</v>
@@ -3168,10 +3189,10 @@
         <v>173</v>
       </c>
       <c r="B78" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C78" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="D78" t="s">
         <v>158</v>
@@ -3187,10 +3208,10 @@
         <v>174</v>
       </c>
       <c r="B79" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C79" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="D79" t="s">
         <v>168</v>
@@ -3206,10 +3227,10 @@
         <v>175</v>
       </c>
       <c r="B80" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C80" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="D80" t="s">
         <v>176</v>
@@ -3225,10 +3246,10 @@
         <v>178</v>
       </c>
       <c r="B81" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C81" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="D81" t="s">
         <v>176</v>
@@ -3244,10 +3265,10 @@
         <v>179</v>
       </c>
       <c r="B82" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C82" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="D82" t="s">
         <v>176</v>
@@ -3263,10 +3284,10 @@
         <v>180</v>
       </c>
       <c r="B83" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C83" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="D83" t="s">
         <v>158</v>
@@ -3282,10 +3303,10 @@
         <v>181</v>
       </c>
       <c r="B84" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C84" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="D84" t="s">
         <v>168</v>
@@ -3301,10 +3322,10 @@
         <v>182</v>
       </c>
       <c r="B85" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C85" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="D85" t="s">
         <v>168</v>
@@ -3320,10 +3341,10 @@
         <v>183</v>
       </c>
       <c r="B86" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C86" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="D86" t="s">
         <v>184</v>
@@ -3339,10 +3360,10 @@
         <v>186</v>
       </c>
       <c r="B87" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C87" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="D87" t="s">
         <v>187</v>
@@ -3358,10 +3379,10 @@
         <v>189</v>
       </c>
       <c r="B88" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C88" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="D88" t="s">
         <v>187</v>
@@ -3377,10 +3398,10 @@
         <v>190</v>
       </c>
       <c r="B89" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C89" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="D89" t="s">
         <v>187</v>
@@ -3396,10 +3417,10 @@
         <v>191</v>
       </c>
       <c r="B90" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C90" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="D90" t="s">
         <v>161</v>
@@ -3415,10 +3436,10 @@
         <v>192</v>
       </c>
       <c r="B91" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C91" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="D91" t="s">
         <v>193</v>
@@ -3434,10 +3455,10 @@
         <v>195</v>
       </c>
       <c r="B92" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C92" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="D92" t="s">
         <v>114</v>
@@ -3453,10 +3474,10 @@
         <v>196</v>
       </c>
       <c r="B93" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C93" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="D93" t="s">
         <v>114</v>
@@ -3472,10 +3493,10 @@
         <v>197</v>
       </c>
       <c r="B94" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C94" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="D94" t="s">
         <v>198</v>
@@ -3491,10 +3512,10 @@
         <v>200</v>
       </c>
       <c r="B95" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C95" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="D95" t="s">
         <v>139</v>
@@ -3510,10 +3531,10 @@
         <v>201</v>
       </c>
       <c r="B96" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C96" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="D96" t="s">
         <v>202</v>
@@ -3529,10 +3550,10 @@
         <v>204</v>
       </c>
       <c r="B97" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C97" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="D97" t="s">
         <v>202</v>
@@ -3548,10 +3569,10 @@
         <v>205</v>
       </c>
       <c r="B98" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C98" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="D98" t="s">
         <v>206</v>
@@ -3567,10 +3588,10 @@
         <v>208</v>
       </c>
       <c r="B99" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C99" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="D99" t="s">
         <v>209</v>
@@ -3586,10 +3607,10 @@
         <v>211</v>
       </c>
       <c r="B100" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C100" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="D100" t="s">
         <v>212</v>
@@ -3605,10 +3626,10 @@
         <v>214</v>
       </c>
       <c r="B101" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C101" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="D101" t="s">
         <v>215</v>
@@ -3624,10 +3645,10 @@
         <v>217</v>
       </c>
       <c r="B102" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C102" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="D102" t="s">
         <v>218</v>
@@ -3643,10 +3664,10 @@
         <v>220</v>
       </c>
       <c r="B103" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C103" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="D103" t="s">
         <v>221</v>
@@ -3662,10 +3683,10 @@
         <v>223</v>
       </c>
       <c r="B104" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C104" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="D104" t="s">
         <v>221</v>
@@ -3681,10 +3702,10 @@
         <v>224</v>
       </c>
       <c r="B105" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C105" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="D105" t="s">
         <v>225</v>
@@ -3700,10 +3721,10 @@
         <v>227</v>
       </c>
       <c r="B106" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C106" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="D106" t="s">
         <v>225</v>
@@ -3719,10 +3740,10 @@
         <v>228</v>
       </c>
       <c r="B107" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C107" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="D107" t="s">
         <v>225</v>
@@ -3738,10 +3759,10 @@
         <v>229</v>
       </c>
       <c r="B108" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C108" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="D108" t="s">
         <v>225</v>
@@ -3757,10 +3778,10 @@
         <v>230</v>
       </c>
       <c r="B109" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C109" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="D109" t="s">
         <v>20</v>
@@ -3776,10 +3797,10 @@
         <v>231</v>
       </c>
       <c r="B110" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C110" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="D110" t="s">
         <v>232</v>
@@ -3795,10 +3816,10 @@
         <v>234</v>
       </c>
       <c r="B111" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C111" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="D111" t="s">
         <v>235</v>
@@ -3814,10 +3835,10 @@
         <v>237</v>
       </c>
       <c r="B112" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C112" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="D112" t="s">
         <v>235</v>
@@ -3833,10 +3854,10 @@
         <v>238</v>
       </c>
       <c r="B113" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C113" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="D113" t="s">
         <v>235</v>
@@ -3852,10 +3873,10 @@
         <v>239</v>
       </c>
       <c r="B114" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C114" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="D114" t="s">
         <v>235</v>
@@ -3871,10 +3892,10 @@
         <v>240</v>
       </c>
       <c r="B115" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C115" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="D115" t="s">
         <v>241</v>
@@ -3890,10 +3911,10 @@
         <v>243</v>
       </c>
       <c r="B116" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C116" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="D116" t="s">
         <v>241</v>
@@ -3909,10 +3930,10 @@
         <v>244</v>
       </c>
       <c r="B117" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C117" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="D117" t="s">
         <v>245</v>
@@ -3928,10 +3949,10 @@
         <v>247</v>
       </c>
       <c r="B118" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C118" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="D118" t="s">
         <v>248</v>
@@ -3947,10 +3968,10 @@
         <v>250</v>
       </c>
       <c r="B119" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C119" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="D119" t="s">
         <v>248</v>
@@ -3966,10 +3987,10 @@
         <v>251</v>
       </c>
       <c r="B120" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C120" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="D120" t="s">
         <v>248</v>
@@ -3985,10 +4006,10 @@
         <v>252</v>
       </c>
       <c r="B121" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C121" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D121" t="s">
         <v>253</v>
@@ -4004,10 +4025,10 @@
         <v>255</v>
       </c>
       <c r="B122" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C122" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D122" t="s">
         <v>253</v>
@@ -4023,10 +4044,10 @@
         <v>256</v>
       </c>
       <c r="B123" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C123" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="D123" t="s">
         <v>257</v>
@@ -4042,10 +4063,10 @@
         <v>259</v>
       </c>
       <c r="B124" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C124" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="D124" t="s">
         <v>257</v>
@@ -4061,10 +4082,10 @@
         <v>260</v>
       </c>
       <c r="B125" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C125" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="D125" t="s">
         <v>257</v>
@@ -4080,10 +4101,10 @@
         <v>261</v>
       </c>
       <c r="B126" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C126" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="D126" t="s">
         <v>248</v>
@@ -4099,10 +4120,10 @@
         <v>262</v>
       </c>
       <c r="B127" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C127" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="D127" t="s">
         <v>263</v>
@@ -4118,10 +4139,10 @@
         <v>265</v>
       </c>
       <c r="B128" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C128" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="D128" t="s">
         <v>158</v>
@@ -4137,10 +4158,10 @@
         <v>266</v>
       </c>
       <c r="B129" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C129" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="D129" t="s">
         <v>29</v>
@@ -4156,10 +4177,10 @@
         <v>267</v>
       </c>
       <c r="B130" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C130" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="D130" t="s">
         <v>120</v>
@@ -4175,10 +4196,10 @@
         <v>268</v>
       </c>
       <c r="B131" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C131" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="D131" t="s">
         <v>269</v>
@@ -4187,7 +4208,7 @@
         <v>270</v>
       </c>
       <c r="F131" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="G131" t="s">
         <v>271</v>
@@ -4201,10 +4222,10 @@
         <v>273</v>
       </c>
       <c r="B132" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C132" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D132" t="s">
         <v>35</v>
@@ -4220,10 +4241,10 @@
         <v>274</v>
       </c>
       <c r="B133" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C133" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="D133" t="s">
         <v>275</v>
@@ -4239,10 +4260,10 @@
         <v>277</v>
       </c>
       <c r="B134" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C134" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="D134" t="s">
         <v>278</v>
@@ -4258,10 +4279,10 @@
         <v>280</v>
       </c>
       <c r="B135" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C135" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="D135" t="s">
         <v>281</v>
@@ -4277,10 +4298,10 @@
         <v>283</v>
       </c>
       <c r="B136" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C136" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D136" t="s">
         <v>281</v>
@@ -4296,10 +4317,10 @@
         <v>285</v>
       </c>
       <c r="B137" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C137" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D137" t="s">
         <v>281</v>
@@ -4315,10 +4336,10 @@
         <v>287</v>
       </c>
       <c r="B138" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C138" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="D138" t="s">
         <v>221</v>
@@ -4334,10 +4355,10 @@
         <v>288</v>
       </c>
       <c r="B139" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C139" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D139" t="s">
         <v>289</v>
@@ -4353,10 +4374,10 @@
         <v>291</v>
       </c>
       <c r="B140" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C140" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="D140" t="s">
         <v>120</v>
@@ -4372,10 +4393,10 @@
         <v>292</v>
       </c>
       <c r="B141" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C141" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="D141" t="s">
         <v>123</v>
@@ -4391,10 +4412,10 @@
         <v>293</v>
       </c>
       <c r="B142" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C142" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="D142" t="s">
         <v>117</v>
@@ -4410,10 +4431,10 @@
         <v>294</v>
       </c>
       <c r="B143" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C143" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D143" t="s">
         <v>35</v>
@@ -4429,10 +4450,10 @@
         <v>295</v>
       </c>
       <c r="B144" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C144" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="D144" t="s">
         <v>38</v>
@@ -4448,10 +4469,10 @@
         <v>296</v>
       </c>
       <c r="B145" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="C145" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="D145" t="s">
         <v>117</v>
@@ -4467,10 +4488,10 @@
         <v>297</v>
       </c>
       <c r="B146" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="C146" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D146" t="s">
         <v>35</v>
@@ -4486,10 +4507,10 @@
         <v>298</v>
       </c>
       <c r="B147" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C147" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="D147" t="s">
         <v>299</v>
@@ -4505,10 +4526,10 @@
         <v>301</v>
       </c>
       <c r="B148" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C148" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="D148" t="s">
         <v>302</v>
@@ -4524,10 +4545,10 @@
         <v>304</v>
       </c>
       <c r="B149" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C149" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="D149" t="s">
         <v>302</v>
@@ -4543,10 +4564,10 @@
         <v>305</v>
       </c>
       <c r="B150" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C150" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="D150" t="s">
         <v>306</v>
@@ -4562,10 +4583,10 @@
         <v>308</v>
       </c>
       <c r="B151" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C151" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="D151" t="s">
         <v>150</v>
@@ -4581,10 +4602,10 @@
         <v>309</v>
       </c>
       <c r="B152" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C152" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="D152" t="s">
         <v>310</v>
@@ -4600,10 +4621,10 @@
         <v>312</v>
       </c>
       <c r="B153" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C153" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="D153" t="s">
         <v>313</v>
@@ -4619,10 +4640,10 @@
         <v>315</v>
       </c>
       <c r="B154" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C154" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D154" t="s">
         <v>316</v>
@@ -4638,10 +4659,10 @@
         <v>318</v>
       </c>
       <c r="B155" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C155" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D155" t="s">
         <v>316</v>
@@ -4657,10 +4678,10 @@
         <v>319</v>
       </c>
       <c r="B156" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C156" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="D156" t="s">
         <v>75</v>
@@ -4676,10 +4697,10 @@
         <v>320</v>
       </c>
       <c r="B157" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C157" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="D157" t="s">
         <v>111</v>
@@ -4695,10 +4716,10 @@
         <v>321</v>
       </c>
       <c r="B158" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C158" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="D158" t="s">
         <v>221</v>
@@ -4714,10 +4735,10 @@
         <v>322</v>
       </c>
       <c r="B159" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C159" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="D159" t="s">
         <v>150</v>
@@ -4733,10 +4754,10 @@
         <v>323</v>
       </c>
       <c r="B160" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C160" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="D160" t="s">
         <v>150</v>
@@ -4752,10 +4773,10 @@
         <v>324</v>
       </c>
       <c r="B161" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C161" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="D161" t="s">
         <v>150</v>
@@ -4771,10 +4792,10 @@
         <v>325</v>
       </c>
       <c r="B162" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C162" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="D162" t="s">
         <v>108</v>
@@ -4790,10 +4811,10 @@
         <v>326</v>
       </c>
       <c r="B163" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C163" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="D163" t="s">
         <v>327</v>
@@ -4809,10 +4830,10 @@
         <v>329</v>
       </c>
       <c r="B164" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C164" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D164" t="s">
         <v>289</v>
@@ -4828,10 +4849,10 @@
         <v>330</v>
       </c>
       <c r="B165" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C165" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="D165" t="s">
         <v>331</v>
@@ -4847,10 +4868,10 @@
         <v>333</v>
       </c>
       <c r="B166" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C166" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="D166" t="s">
         <v>334</v>
@@ -4866,10 +4887,10 @@
         <v>336</v>
       </c>
       <c r="B167" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C167" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="D167" t="s">
         <v>334</v>
@@ -4885,10 +4906,10 @@
         <v>337</v>
       </c>
       <c r="B168" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C168" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="D168" t="s">
         <v>338</v>
@@ -4904,10 +4925,10 @@
         <v>340</v>
       </c>
       <c r="B169" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C169" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="D169" t="s">
         <v>341</v>
@@ -4923,10 +4944,10 @@
         <v>343</v>
       </c>
       <c r="B170" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C170" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="D170" t="s">
         <v>344</v>
@@ -4942,10 +4963,10 @@
         <v>346</v>
       </c>
       <c r="B171" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="C171" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="D171" t="s">
         <v>347</v>
@@ -4961,10 +4982,10 @@
         <v>349</v>
       </c>
       <c r="B172" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C172" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="D172" t="s">
         <v>139</v>
@@ -4980,10 +5001,10 @@
         <v>350</v>
       </c>
       <c r="B173" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C173" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="D173" t="s">
         <v>139</v>
@@ -4999,10 +5020,10 @@
         <v>351</v>
       </c>
       <c r="B174" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C174" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="D174" t="s">
         <v>352</v>
@@ -5018,10 +5039,10 @@
         <v>354</v>
       </c>
       <c r="B175" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="C175" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="D175" t="s">
         <v>355</v>
@@ -5037,10 +5058,10 @@
         <v>357</v>
       </c>
       <c r="B176" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="C176" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="D176" t="s">
         <v>355</v>
@@ -5056,10 +5077,10 @@
         <v>358</v>
       </c>
       <c r="B177" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="C177" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="D177" t="s">
         <v>359</v>
@@ -5075,10 +5096,10 @@
         <v>361</v>
       </c>
       <c r="B178" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="C178" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="D178" t="s">
         <v>29</v>
@@ -5094,10 +5115,10 @@
         <v>362</v>
       </c>
       <c r="B179" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="C179" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="D179" t="s">
         <v>29</v>
@@ -5113,10 +5134,10 @@
         <v>363</v>
       </c>
       <c r="B180" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="C180" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="D180" t="s">
         <v>29</v>
@@ -5132,10 +5153,10 @@
         <v>364</v>
       </c>
       <c r="B181" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="C181" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="D181" t="s">
         <v>29</v>
@@ -5151,10 +5172,10 @@
         <v>365</v>
       </c>
       <c r="B182" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="C182" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="D182" t="s">
         <v>29</v>
@@ -5170,10 +5191,10 @@
         <v>366</v>
       </c>
       <c r="B183" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="C183" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="D183" t="s">
         <v>29</v>
@@ -5189,10 +5210,10 @@
         <v>367</v>
       </c>
       <c r="B184" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="C184" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="D184" t="s">
         <v>29</v>
@@ -5208,10 +5229,10 @@
         <v>368</v>
       </c>
       <c r="B185" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="C185" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="D185" t="s">
         <v>29</v>
@@ -5227,10 +5248,10 @@
         <v>369</v>
       </c>
       <c r="B186" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C186" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="D186" t="s">
         <v>29</v>
@@ -5246,10 +5267,10 @@
         <v>370</v>
       </c>
       <c r="B187" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C187" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="D187" t="s">
         <v>29</v>
@@ -5265,10 +5286,10 @@
         <v>371</v>
       </c>
       <c r="B188" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C188" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="D188" t="s">
         <v>14</v>
@@ -5284,10 +5305,10 @@
         <v>372</v>
       </c>
       <c r="B189" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C189" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="D189" t="s">
         <v>373</v>
@@ -5303,10 +5324,10 @@
         <v>375</v>
       </c>
       <c r="B190" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C190" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="D190" t="s">
         <v>376</v>
@@ -5322,10 +5343,10 @@
         <v>378</v>
       </c>
       <c r="B191" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C191" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="D191" t="s">
         <v>376</v>
@@ -5341,10 +5362,10 @@
         <v>379</v>
       </c>
       <c r="B192" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C192" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="D192" t="s">
         <v>380</v>
@@ -5360,10 +5381,10 @@
         <v>382</v>
       </c>
       <c r="B193" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C193" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="D193" t="s">
         <v>383</v>
@@ -5379,10 +5400,10 @@
         <v>385</v>
       </c>
       <c r="B194" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C194" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="D194" t="s">
         <v>386</v>
@@ -5398,10 +5419,10 @@
         <v>388</v>
       </c>
       <c r="B195" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C195" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="D195" t="s">
         <v>389</v>
@@ -5417,10 +5438,10 @@
         <v>391</v>
       </c>
       <c r="B196" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C196" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="D196" t="s">
         <v>392</v>
@@ -5436,10 +5457,10 @@
         <v>394</v>
       </c>
       <c r="B197" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C197" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="D197" t="s">
         <v>395</v>
@@ -5455,10 +5476,10 @@
         <v>397</v>
       </c>
       <c r="B198" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C198" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D198" t="s">
         <v>398</v>
@@ -5474,10 +5495,10 @@
         <v>400</v>
       </c>
       <c r="B199" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C199" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="D199" t="s">
         <v>401</v>
@@ -5493,10 +5514,10 @@
         <v>403</v>
       </c>
       <c r="B200" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C200" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="D200" t="s">
         <v>404</v>
@@ -5512,10 +5533,10 @@
         <v>406</v>
       </c>
       <c r="B201" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C201" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="D201" t="s">
         <v>407</v>
@@ -5531,10 +5552,10 @@
         <v>409</v>
       </c>
       <c r="B202" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C202" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="D202" t="s">
         <v>410</v>
@@ -5550,10 +5571,10 @@
         <v>412</v>
       </c>
       <c r="B203" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C203" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="D203" t="s">
         <v>413</v>
@@ -5569,10 +5590,10 @@
         <v>415</v>
       </c>
       <c r="B204" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="C204" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="D204" t="s">
         <v>59</v>
@@ -5582,6 +5603,54 @@
       </c>
       <c r="G204"/>
       <c r="H204"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>416</v>
+      </c>
+      <c r="B205" t="s">
+        <v>9</v>
+      </c>
+      <c r="D205" t="s">
+        <v>417</v>
+      </c>
+      <c r="E205" t="s">
+        <v>418</v>
+      </c>
+      <c r="G205"/>
+      <c r="H205"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>419</v>
+      </c>
+      <c r="B206" t="s">
+        <v>9</v>
+      </c>
+      <c r="D206" t="s">
+        <v>417</v>
+      </c>
+      <c r="E206" t="s">
+        <v>418</v>
+      </c>
+      <c r="G206"/>
+      <c r="H206"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>420</v>
+      </c>
+      <c r="B207" t="s">
+        <v>9</v>
+      </c>
+      <c r="D207" t="s">
+        <v>421</v>
+      </c>
+      <c r="E207" t="s">
+        <v>422</v>
+      </c>
+      <c r="G207"/>
+      <c r="H207"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>

--- a/Mod_Korean/Lang/KR/Game/Block.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Block.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252</t>
+    <t xml:space="preserve">EA 23.260</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>

--- a/Mod_Korean/Lang/KR/Game/Block.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Block.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.260</t>
+    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>

--- a/Mod_Korean/Lang/KR/Game/Block.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Block.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.281</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>

--- a/Mod_Korean/Lang/KR/Game/Block.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Block.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.281</t>
+    <t xml:space="preserve">EA 23.282 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>

--- a/Mod_Korean/Lang/KR/Game/Block.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Block.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="556">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282 Patch 2</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
@@ -1284,6 +1284,24 @@
   </si>
   <si>
     <t xml:space="preserve">石のフェンス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cloud block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雲のブロック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alien block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エイリアンのブロック</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 11.1</t>
@@ -1770,7 +1788,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -1782,10 +1800,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C4" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1801,10 +1819,10 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C5" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -1820,10 +1838,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C6" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -1839,10 +1857,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C7" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -1858,10 +1876,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C8" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
@@ -1877,10 +1895,10 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C9" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -1896,10 +1914,10 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C10" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -1915,10 +1933,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C11" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -1934,10 +1952,10 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C12" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
@@ -1953,10 +1971,10 @@
         <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C13" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
@@ -1972,10 +1990,10 @@
         <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C14" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
@@ -1991,10 +2009,10 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C15" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="D15" t="s">
         <v>44</v>
@@ -2010,10 +2028,10 @@
         <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C16" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="D16" t="s">
         <v>47</v>
@@ -2022,7 +2040,7 @@
         <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="G16"/>
       <c r="H16" t="s">
@@ -2034,10 +2052,10 @@
         <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C17" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="D17" t="s">
         <v>44</v>
@@ -2053,10 +2071,10 @@
         <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C18" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="D18" t="s">
         <v>52</v>
@@ -2072,10 +2090,10 @@
         <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C19" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D19" t="s">
         <v>35</v>
@@ -2091,10 +2109,10 @@
         <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C20" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="D20" t="s">
         <v>56</v>
@@ -2110,10 +2128,10 @@
         <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C21" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="D21" t="s">
         <v>59</v>
@@ -2129,10 +2147,10 @@
         <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C22" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D22" t="s">
         <v>35</v>
@@ -2148,10 +2166,10 @@
         <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C23" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D23" t="s">
         <v>35</v>
@@ -2167,10 +2185,10 @@
         <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C24" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D24" t="s">
         <v>35</v>
@@ -2186,10 +2204,10 @@
         <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C25" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="D25" t="s">
         <v>65</v>
@@ -2205,10 +2223,10 @@
         <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C26" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="D26" t="s">
         <v>52</v>
@@ -2224,10 +2242,10 @@
         <v>68</v>
       </c>
       <c r="B27" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C27" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="D27" t="s">
         <v>69</v>
@@ -2243,10 +2261,10 @@
         <v>71</v>
       </c>
       <c r="B28" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C28" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="D28" t="s">
         <v>72</v>
@@ -2262,10 +2280,10 @@
         <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C29" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="D29" t="s">
         <v>75</v>
@@ -2281,10 +2299,10 @@
         <v>77</v>
       </c>
       <c r="B30" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C30" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
@@ -2300,10 +2318,10 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C31" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="D31" t="s">
         <v>47</v>
@@ -2312,7 +2330,7 @@
         <v>48</v>
       </c>
       <c r="F31" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="G31"/>
       <c r="H31" t="s">
@@ -2324,10 +2342,10 @@
         <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C32" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D32" t="s">
         <v>80</v>
@@ -2343,10 +2361,10 @@
         <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C33" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="D33" t="s">
         <v>83</v>
@@ -2362,10 +2380,10 @@
         <v>85</v>
       </c>
       <c r="B34" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C34" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="D34" t="s">
         <v>83</v>
@@ -2381,10 +2399,10 @@
         <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C35" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="D35" t="s">
         <v>83</v>
@@ -2400,10 +2418,10 @@
         <v>87</v>
       </c>
       <c r="B36" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C36" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="D36" t="s">
         <v>88</v>
@@ -2419,10 +2437,10 @@
         <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C37" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="D37" t="s">
         <v>91</v>
@@ -2438,10 +2456,10 @@
         <v>93</v>
       </c>
       <c r="B38" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C38" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="D38" t="s">
         <v>94</v>
@@ -2457,10 +2475,10 @@
         <v>96</v>
       </c>
       <c r="B39" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C39" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="D39" t="s">
         <v>97</v>
@@ -2476,10 +2494,10 @@
         <v>99</v>
       </c>
       <c r="B40" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C40" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="D40" t="s">
         <v>29</v>
@@ -2495,10 +2513,10 @@
         <v>100</v>
       </c>
       <c r="B41" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C41" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="D41" t="s">
         <v>29</v>
@@ -2514,10 +2532,10 @@
         <v>101</v>
       </c>
       <c r="B42" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C42" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="D42" t="s">
         <v>29</v>
@@ -2533,10 +2551,10 @@
         <v>102</v>
       </c>
       <c r="B43" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C43" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="D43" t="s">
         <v>29</v>
@@ -2552,10 +2570,10 @@
         <v>103</v>
       </c>
       <c r="B44" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C44" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="D44" t="s">
         <v>29</v>
@@ -2571,10 +2589,10 @@
         <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C45" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
@@ -2590,10 +2608,10 @@
         <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C46" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="D46" t="s">
         <v>75</v>
@@ -2609,10 +2627,10 @@
         <v>106</v>
       </c>
       <c r="B47" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C47" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D47" t="s">
         <v>14</v>
@@ -2628,10 +2646,10 @@
         <v>107</v>
       </c>
       <c r="B48" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C48" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="D48" t="s">
         <v>108</v>
@@ -2647,10 +2665,10 @@
         <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C49" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D49" t="s">
         <v>111</v>
@@ -2666,10 +2684,10 @@
         <v>113</v>
       </c>
       <c r="B50" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C50" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="D50" t="s">
         <v>114</v>
@@ -2685,10 +2703,10 @@
         <v>116</v>
       </c>
       <c r="B51" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C51" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="D51" t="s">
         <v>117</v>
@@ -2704,10 +2722,10 @@
         <v>119</v>
       </c>
       <c r="B52" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C52" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D52" t="s">
         <v>120</v>
@@ -2723,10 +2741,10 @@
         <v>122</v>
       </c>
       <c r="B53" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C53" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D53" t="s">
         <v>123</v>
@@ -2742,10 +2760,10 @@
         <v>125</v>
       </c>
       <c r="B54" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C54" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="D54" t="s">
         <v>126</v>
@@ -2761,10 +2779,10 @@
         <v>128</v>
       </c>
       <c r="B55" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C55" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="D55" t="s">
         <v>129</v>
@@ -2780,10 +2798,10 @@
         <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C56" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="D56" t="s">
         <v>132</v>
@@ -2799,10 +2817,10 @@
         <v>134</v>
       </c>
       <c r="B57" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C57" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="D57" t="s">
         <v>135</v>
@@ -2818,10 +2836,10 @@
         <v>137</v>
       </c>
       <c r="B58" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C58" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="D58" t="s">
         <v>117</v>
@@ -2837,10 +2855,10 @@
         <v>138</v>
       </c>
       <c r="B59" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C59" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="D59" t="s">
         <v>139</v>
@@ -2856,10 +2874,10 @@
         <v>141</v>
       </c>
       <c r="B60" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C60" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="D60" t="s">
         <v>142</v>
@@ -2875,10 +2893,10 @@
         <v>144</v>
       </c>
       <c r="B61" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C61" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="D61" t="s">
         <v>142</v>
@@ -2894,10 +2912,10 @@
         <v>145</v>
       </c>
       <c r="B62" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C62" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="D62" t="s">
         <v>142</v>
@@ -2913,10 +2931,10 @@
         <v>146</v>
       </c>
       <c r="B63" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C63" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D63" t="s">
         <v>147</v>
@@ -2932,10 +2950,10 @@
         <v>149</v>
       </c>
       <c r="B64" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C64" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D64" t="s">
         <v>150</v>
@@ -2951,10 +2969,10 @@
         <v>152</v>
       </c>
       <c r="B65" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C65" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D65" t="s">
         <v>150</v>
@@ -2970,10 +2988,10 @@
         <v>153</v>
       </c>
       <c r="B66" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C66" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D66" t="s">
         <v>150</v>
@@ -2989,10 +3007,10 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C67" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D67" t="s">
         <v>120</v>
@@ -3008,10 +3026,10 @@
         <v>155</v>
       </c>
       <c r="B68" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C68" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D68" t="s">
         <v>14</v>
@@ -3027,10 +3045,10 @@
         <v>156</v>
       </c>
       <c r="B69" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C69" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D69" t="s">
         <v>14</v>
@@ -3046,10 +3064,10 @@
         <v>157</v>
       </c>
       <c r="B70" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C70" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D70" t="s">
         <v>158</v>
@@ -3065,10 +3083,10 @@
         <v>160</v>
       </c>
       <c r="B71" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C71" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D71" t="s">
         <v>161</v>
@@ -3084,10 +3102,10 @@
         <v>163</v>
       </c>
       <c r="B72" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C72" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D72" t="s">
         <v>158</v>
@@ -3103,10 +3121,10 @@
         <v>164</v>
       </c>
       <c r="B73" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C73" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="D73" t="s">
         <v>165</v>
@@ -3122,10 +3140,10 @@
         <v>167</v>
       </c>
       <c r="B74" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C74" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="D74" t="s">
         <v>168</v>
@@ -3141,10 +3159,10 @@
         <v>170</v>
       </c>
       <c r="B75" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C75" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="D75" t="s">
         <v>168</v>
@@ -3160,10 +3178,10 @@
         <v>171</v>
       </c>
       <c r="B76" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C76" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D76" t="s">
         <v>158</v>
@@ -3179,10 +3197,10 @@
         <v>172</v>
       </c>
       <c r="B77" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C77" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="D77" t="s">
         <v>168</v>
@@ -3198,10 +3216,10 @@
         <v>173</v>
       </c>
       <c r="B78" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C78" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D78" t="s">
         <v>158</v>
@@ -3217,10 +3235,10 @@
         <v>174</v>
       </c>
       <c r="B79" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C79" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="D79" t="s">
         <v>168</v>
@@ -3236,10 +3254,10 @@
         <v>175</v>
       </c>
       <c r="B80" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C80" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="D80" t="s">
         <v>176</v>
@@ -3255,10 +3273,10 @@
         <v>178</v>
       </c>
       <c r="B81" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C81" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="D81" t="s">
         <v>176</v>
@@ -3274,10 +3292,10 @@
         <v>179</v>
       </c>
       <c r="B82" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C82" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="D82" t="s">
         <v>176</v>
@@ -3293,10 +3311,10 @@
         <v>180</v>
       </c>
       <c r="B83" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C83" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D83" t="s">
         <v>158</v>
@@ -3312,10 +3330,10 @@
         <v>181</v>
       </c>
       <c r="B84" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C84" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="D84" t="s">
         <v>168</v>
@@ -3331,10 +3349,10 @@
         <v>182</v>
       </c>
       <c r="B85" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C85" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="D85" t="s">
         <v>168</v>
@@ -3350,10 +3368,10 @@
         <v>183</v>
       </c>
       <c r="B86" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C86" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="D86" t="s">
         <v>184</v>
@@ -3369,10 +3387,10 @@
         <v>186</v>
       </c>
       <c r="B87" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C87" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="D87" t="s">
         <v>187</v>
@@ -3388,10 +3406,10 @@
         <v>189</v>
       </c>
       <c r="B88" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C88" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="D88" t="s">
         <v>187</v>
@@ -3407,10 +3425,10 @@
         <v>190</v>
       </c>
       <c r="B89" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C89" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="D89" t="s">
         <v>187</v>
@@ -3426,10 +3444,10 @@
         <v>191</v>
       </c>
       <c r="B90" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C90" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D90" t="s">
         <v>161</v>
@@ -3445,10 +3463,10 @@
         <v>192</v>
       </c>
       <c r="B91" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C91" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="D91" t="s">
         <v>193</v>
@@ -3464,10 +3482,10 @@
         <v>195</v>
       </c>
       <c r="B92" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C92" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="D92" t="s">
         <v>114</v>
@@ -3483,10 +3501,10 @@
         <v>196</v>
       </c>
       <c r="B93" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C93" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="D93" t="s">
         <v>114</v>
@@ -3502,10 +3520,10 @@
         <v>197</v>
       </c>
       <c r="B94" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C94" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="D94" t="s">
         <v>198</v>
@@ -3521,10 +3539,10 @@
         <v>200</v>
       </c>
       <c r="B95" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C95" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="D95" t="s">
         <v>139</v>
@@ -3540,10 +3558,10 @@
         <v>201</v>
       </c>
       <c r="B96" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C96" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="D96" t="s">
         <v>202</v>
@@ -3559,10 +3577,10 @@
         <v>204</v>
       </c>
       <c r="B97" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C97" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="D97" t="s">
         <v>202</v>
@@ -3578,10 +3596,10 @@
         <v>205</v>
       </c>
       <c r="B98" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C98" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="D98" t="s">
         <v>206</v>
@@ -3597,10 +3615,10 @@
         <v>208</v>
       </c>
       <c r="B99" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C99" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="D99" t="s">
         <v>209</v>
@@ -3616,10 +3634,10 @@
         <v>211</v>
       </c>
       <c r="B100" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C100" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D100" t="s">
         <v>212</v>
@@ -3635,10 +3653,10 @@
         <v>214</v>
       </c>
       <c r="B101" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C101" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D101" t="s">
         <v>215</v>
@@ -3654,10 +3672,10 @@
         <v>217</v>
       </c>
       <c r="B102" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C102" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="D102" t="s">
         <v>218</v>
@@ -3673,10 +3691,10 @@
         <v>220</v>
       </c>
       <c r="B103" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C103" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D103" t="s">
         <v>221</v>
@@ -3692,10 +3710,10 @@
         <v>223</v>
       </c>
       <c r="B104" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C104" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D104" t="s">
         <v>221</v>
@@ -3711,10 +3729,10 @@
         <v>224</v>
       </c>
       <c r="B105" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C105" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D105" t="s">
         <v>225</v>
@@ -3730,10 +3748,10 @@
         <v>227</v>
       </c>
       <c r="B106" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C106" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D106" t="s">
         <v>225</v>
@@ -3749,10 +3767,10 @@
         <v>228</v>
       </c>
       <c r="B107" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C107" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D107" t="s">
         <v>225</v>
@@ -3768,10 +3786,10 @@
         <v>229</v>
       </c>
       <c r="B108" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C108" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D108" t="s">
         <v>225</v>
@@ -3787,10 +3805,10 @@
         <v>230</v>
       </c>
       <c r="B109" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C109" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D109" t="s">
         <v>20</v>
@@ -3806,10 +3824,10 @@
         <v>231</v>
       </c>
       <c r="B110" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C110" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="D110" t="s">
         <v>232</v>
@@ -3825,10 +3843,10 @@
         <v>234</v>
       </c>
       <c r="B111" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C111" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D111" t="s">
         <v>235</v>
@@ -3844,10 +3862,10 @@
         <v>237</v>
       </c>
       <c r="B112" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C112" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D112" t="s">
         <v>235</v>
@@ -3863,10 +3881,10 @@
         <v>238</v>
       </c>
       <c r="B113" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C113" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D113" t="s">
         <v>235</v>
@@ -3882,10 +3900,10 @@
         <v>239</v>
       </c>
       <c r="B114" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C114" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D114" t="s">
         <v>235</v>
@@ -3901,10 +3919,10 @@
         <v>240</v>
       </c>
       <c r="B115" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C115" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D115" t="s">
         <v>241</v>
@@ -3920,10 +3938,10 @@
         <v>243</v>
       </c>
       <c r="B116" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C116" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D116" t="s">
         <v>241</v>
@@ -3939,10 +3957,10 @@
         <v>244</v>
       </c>
       <c r="B117" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C117" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D117" t="s">
         <v>245</v>
@@ -3958,10 +3976,10 @@
         <v>247</v>
       </c>
       <c r="B118" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C118" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="D118" t="s">
         <v>248</v>
@@ -3977,10 +3995,10 @@
         <v>250</v>
       </c>
       <c r="B119" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C119" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="D119" t="s">
         <v>248</v>
@@ -3996,10 +4014,10 @@
         <v>251</v>
       </c>
       <c r="B120" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C120" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="D120" t="s">
         <v>248</v>
@@ -4015,10 +4033,10 @@
         <v>252</v>
       </c>
       <c r="B121" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C121" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="D121" t="s">
         <v>253</v>
@@ -4034,10 +4052,10 @@
         <v>255</v>
       </c>
       <c r="B122" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C122" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="D122" t="s">
         <v>253</v>
@@ -4053,10 +4071,10 @@
         <v>256</v>
       </c>
       <c r="B123" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C123" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D123" t="s">
         <v>257</v>
@@ -4072,10 +4090,10 @@
         <v>259</v>
       </c>
       <c r="B124" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C124" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D124" t="s">
         <v>257</v>
@@ -4091,10 +4109,10 @@
         <v>260</v>
       </c>
       <c r="B125" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C125" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D125" t="s">
         <v>257</v>
@@ -4110,10 +4128,10 @@
         <v>261</v>
       </c>
       <c r="B126" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C126" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="D126" t="s">
         <v>248</v>
@@ -4129,10 +4147,10 @@
         <v>262</v>
       </c>
       <c r="B127" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C127" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="D127" t="s">
         <v>263</v>
@@ -4148,10 +4166,10 @@
         <v>265</v>
       </c>
       <c r="B128" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C128" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D128" t="s">
         <v>158</v>
@@ -4167,10 +4185,10 @@
         <v>266</v>
       </c>
       <c r="B129" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C129" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="D129" t="s">
         <v>29</v>
@@ -4186,10 +4204,10 @@
         <v>267</v>
       </c>
       <c r="B130" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C130" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D130" t="s">
         <v>120</v>
@@ -4205,10 +4223,10 @@
         <v>268</v>
       </c>
       <c r="B131" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C131" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="D131" t="s">
         <v>269</v>
@@ -4217,7 +4235,7 @@
         <v>270</v>
       </c>
       <c r="F131" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="G131" t="s">
         <v>271</v>
@@ -4231,10 +4249,10 @@
         <v>273</v>
       </c>
       <c r="B132" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C132" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D132" t="s">
         <v>35</v>
@@ -4250,10 +4268,10 @@
         <v>274</v>
       </c>
       <c r="B133" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C133" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="D133" t="s">
         <v>275</v>
@@ -4269,10 +4287,10 @@
         <v>277</v>
       </c>
       <c r="B134" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C134" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="D134" t="s">
         <v>278</v>
@@ -4288,10 +4306,10 @@
         <v>280</v>
       </c>
       <c r="B135" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C135" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="D135" t="s">
         <v>281</v>
@@ -4307,10 +4325,10 @@
         <v>283</v>
       </c>
       <c r="B136" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C136" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="D136" t="s">
         <v>281</v>
@@ -4326,10 +4344,10 @@
         <v>285</v>
       </c>
       <c r="B137" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C137" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="D137" t="s">
         <v>281</v>
@@ -4345,10 +4363,10 @@
         <v>287</v>
       </c>
       <c r="B138" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C138" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D138" t="s">
         <v>221</v>
@@ -4364,10 +4382,10 @@
         <v>288</v>
       </c>
       <c r="B139" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C139" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="D139" t="s">
         <v>289</v>
@@ -4383,10 +4401,10 @@
         <v>291</v>
       </c>
       <c r="B140" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C140" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D140" t="s">
         <v>120</v>
@@ -4402,10 +4420,10 @@
         <v>292</v>
       </c>
       <c r="B141" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C141" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D141" t="s">
         <v>123</v>
@@ -4421,10 +4439,10 @@
         <v>293</v>
       </c>
       <c r="B142" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C142" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="D142" t="s">
         <v>117</v>
@@ -4440,10 +4458,10 @@
         <v>294</v>
       </c>
       <c r="B143" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C143" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D143" t="s">
         <v>35</v>
@@ -4459,10 +4477,10 @@
         <v>295</v>
       </c>
       <c r="B144" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C144" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D144" t="s">
         <v>38</v>
@@ -4478,10 +4496,10 @@
         <v>296</v>
       </c>
       <c r="B145" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C145" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="D145" t="s">
         <v>117</v>
@@ -4497,10 +4515,10 @@
         <v>297</v>
       </c>
       <c r="B146" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C146" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D146" t="s">
         <v>35</v>
@@ -4516,10 +4534,10 @@
         <v>298</v>
       </c>
       <c r="B147" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C147" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="D147" t="s">
         <v>299</v>
@@ -4535,10 +4553,10 @@
         <v>301</v>
       </c>
       <c r="B148" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C148" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D148" t="s">
         <v>302</v>
@@ -4554,10 +4572,10 @@
         <v>304</v>
       </c>
       <c r="B149" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C149" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D149" t="s">
         <v>302</v>
@@ -4573,10 +4591,10 @@
         <v>305</v>
       </c>
       <c r="B150" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C150" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="D150" t="s">
         <v>306</v>
@@ -4592,10 +4610,10 @@
         <v>308</v>
       </c>
       <c r="B151" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C151" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D151" t="s">
         <v>150</v>
@@ -4611,10 +4629,10 @@
         <v>309</v>
       </c>
       <c r="B152" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C152" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D152" t="s">
         <v>310</v>
@@ -4630,10 +4648,10 @@
         <v>312</v>
       </c>
       <c r="B153" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C153" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="D153" t="s">
         <v>313</v>
@@ -4649,10 +4667,10 @@
         <v>315</v>
       </c>
       <c r="B154" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C154" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="D154" t="s">
         <v>316</v>
@@ -4668,10 +4686,10 @@
         <v>318</v>
       </c>
       <c r="B155" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C155" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="D155" t="s">
         <v>316</v>
@@ -4687,10 +4705,10 @@
         <v>319</v>
       </c>
       <c r="B156" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C156" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="D156" t="s">
         <v>75</v>
@@ -4706,10 +4724,10 @@
         <v>320</v>
       </c>
       <c r="B157" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C157" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D157" t="s">
         <v>111</v>
@@ -4725,10 +4743,10 @@
         <v>321</v>
       </c>
       <c r="B158" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C158" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D158" t="s">
         <v>221</v>
@@ -4744,10 +4762,10 @@
         <v>322</v>
       </c>
       <c r="B159" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C159" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D159" t="s">
         <v>150</v>
@@ -4763,10 +4781,10 @@
         <v>323</v>
       </c>
       <c r="B160" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C160" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D160" t="s">
         <v>150</v>
@@ -4782,10 +4800,10 @@
         <v>324</v>
       </c>
       <c r="B161" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C161" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D161" t="s">
         <v>150</v>
@@ -4801,10 +4819,10 @@
         <v>325</v>
       </c>
       <c r="B162" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C162" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="D162" t="s">
         <v>108</v>
@@ -4820,10 +4838,10 @@
         <v>326</v>
       </c>
       <c r="B163" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C163" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="D163" t="s">
         <v>327</v>
@@ -4839,10 +4857,10 @@
         <v>329</v>
       </c>
       <c r="B164" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C164" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="D164" t="s">
         <v>289</v>
@@ -4858,10 +4876,10 @@
         <v>330</v>
       </c>
       <c r="B165" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C165" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D165" t="s">
         <v>331</v>
@@ -4877,10 +4895,10 @@
         <v>333</v>
       </c>
       <c r="B166" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C166" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="D166" t="s">
         <v>334</v>
@@ -4896,10 +4914,10 @@
         <v>336</v>
       </c>
       <c r="B167" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C167" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="D167" t="s">
         <v>334</v>
@@ -4915,10 +4933,10 @@
         <v>337</v>
       </c>
       <c r="B168" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C168" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="D168" t="s">
         <v>338</v>
@@ -4934,10 +4952,10 @@
         <v>340</v>
       </c>
       <c r="B169" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C169" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="D169" t="s">
         <v>341</v>
@@ -4953,10 +4971,10 @@
         <v>343</v>
       </c>
       <c r="B170" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C170" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D170" t="s">
         <v>344</v>
@@ -4972,10 +4990,10 @@
         <v>346</v>
       </c>
       <c r="B171" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C171" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="D171" t="s">
         <v>347</v>
@@ -4991,10 +5009,10 @@
         <v>349</v>
       </c>
       <c r="B172" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C172" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="D172" t="s">
         <v>139</v>
@@ -5010,10 +5028,10 @@
         <v>350</v>
       </c>
       <c r="B173" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C173" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="D173" t="s">
         <v>139</v>
@@ -5029,10 +5047,10 @@
         <v>351</v>
       </c>
       <c r="B174" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C174" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="D174" t="s">
         <v>352</v>
@@ -5048,10 +5066,10 @@
         <v>354</v>
       </c>
       <c r="B175" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C175" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="D175" t="s">
         <v>355</v>
@@ -5067,10 +5085,10 @@
         <v>357</v>
       </c>
       <c r="B176" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C176" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="D176" t="s">
         <v>355</v>
@@ -5086,10 +5104,10 @@
         <v>358</v>
       </c>
       <c r="B177" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C177" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="D177" t="s">
         <v>359</v>
@@ -5105,10 +5123,10 @@
         <v>361</v>
       </c>
       <c r="B178" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C178" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D178" t="s">
         <v>29</v>
@@ -5124,10 +5142,10 @@
         <v>362</v>
       </c>
       <c r="B179" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C179" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D179" t="s">
         <v>29</v>
@@ -5143,10 +5161,10 @@
         <v>363</v>
       </c>
       <c r="B180" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C180" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D180" t="s">
         <v>29</v>
@@ -5162,10 +5180,10 @@
         <v>364</v>
       </c>
       <c r="B181" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C181" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D181" t="s">
         <v>29</v>
@@ -5181,10 +5199,10 @@
         <v>365</v>
       </c>
       <c r="B182" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C182" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D182" t="s">
         <v>29</v>
@@ -5200,10 +5218,10 @@
         <v>366</v>
       </c>
       <c r="B183" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C183" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D183" t="s">
         <v>29</v>
@@ -5219,10 +5237,10 @@
         <v>367</v>
       </c>
       <c r="B184" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C184" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D184" t="s">
         <v>29</v>
@@ -5238,10 +5256,10 @@
         <v>368</v>
       </c>
       <c r="B185" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C185" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D185" t="s">
         <v>29</v>
@@ -5257,10 +5275,10 @@
         <v>369</v>
       </c>
       <c r="B186" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C186" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D186" t="s">
         <v>29</v>
@@ -5276,10 +5294,10 @@
         <v>370</v>
       </c>
       <c r="B187" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C187" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D187" t="s">
         <v>29</v>
@@ -5295,10 +5313,10 @@
         <v>371</v>
       </c>
       <c r="B188" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C188" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D188" t="s">
         <v>14</v>
@@ -5314,10 +5332,10 @@
         <v>372</v>
       </c>
       <c r="B189" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C189" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="D189" t="s">
         <v>373</v>
@@ -5333,10 +5351,10 @@
         <v>375</v>
       </c>
       <c r="B190" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C190" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="D190" t="s">
         <v>376</v>
@@ -5352,10 +5370,10 @@
         <v>378</v>
       </c>
       <c r="B191" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C191" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="D191" t="s">
         <v>376</v>
@@ -5371,10 +5389,10 @@
         <v>379</v>
       </c>
       <c r="B192" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C192" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="D192" t="s">
         <v>380</v>
@@ -5390,10 +5408,10 @@
         <v>382</v>
       </c>
       <c r="B193" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C193" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="D193" t="s">
         <v>383</v>
@@ -5409,10 +5427,10 @@
         <v>385</v>
       </c>
       <c r="B194" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C194" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="D194" t="s">
         <v>386</v>
@@ -5428,10 +5446,10 @@
         <v>388</v>
       </c>
       <c r="B195" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C195" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="D195" t="s">
         <v>389</v>
@@ -5447,10 +5465,10 @@
         <v>391</v>
       </c>
       <c r="B196" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C196" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="D196" t="s">
         <v>392</v>
@@ -5466,10 +5484,10 @@
         <v>394</v>
       </c>
       <c r="B197" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C197" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D197" t="s">
         <v>395</v>
@@ -5485,10 +5503,10 @@
         <v>397</v>
       </c>
       <c r="B198" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C198" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="D198" t="s">
         <v>398</v>
@@ -5504,10 +5522,10 @@
         <v>400</v>
       </c>
       <c r="B199" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C199" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="D199" t="s">
         <v>401</v>
@@ -5523,10 +5541,10 @@
         <v>403</v>
       </c>
       <c r="B200" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C200" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D200" t="s">
         <v>404</v>
@@ -5542,10 +5560,10 @@
         <v>406</v>
       </c>
       <c r="B201" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C201" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="D201" t="s">
         <v>407</v>
@@ -5561,10 +5579,10 @@
         <v>409</v>
       </c>
       <c r="B202" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C202" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="D202" t="s">
         <v>410</v>
@@ -5580,10 +5598,10 @@
         <v>412</v>
       </c>
       <c r="B203" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C203" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="D203" t="s">
         <v>413</v>
@@ -5599,10 +5617,10 @@
         <v>415</v>
       </c>
       <c r="B204" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C204" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="D204" t="s">
         <v>59</v>
@@ -5618,10 +5636,10 @@
         <v>416</v>
       </c>
       <c r="B205" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C205" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="D205" t="s">
         <v>417</v>
@@ -5637,10 +5655,10 @@
         <v>419</v>
       </c>
       <c r="B206" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C206" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="D206" t="s">
         <v>417</v>
@@ -5656,10 +5674,10 @@
         <v>420</v>
       </c>
       <c r="B207" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C207" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="D207" t="s">
         <v>421</v>
@@ -5669,6 +5687,38 @@
       </c>
       <c r="G207"/>
       <c r="H207"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>423</v>
+      </c>
+      <c r="B208" t="s">
+        <v>9</v>
+      </c>
+      <c r="D208" t="s">
+        <v>424</v>
+      </c>
+      <c r="E208" t="s">
+        <v>425</v>
+      </c>
+      <c r="G208"/>
+      <c r="H208"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>426</v>
+      </c>
+      <c r="B209" t="s">
+        <v>9</v>
+      </c>
+      <c r="D209" t="s">
+        <v>427</v>
+      </c>
+      <c r="E209" t="s">
+        <v>428</v>
+      </c>
+      <c r="G209"/>
+      <c r="H209"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>

--- a/Mod_Korean/Lang/KR/Game/Block.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Block.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.307</t>
+    <t xml:space="preserve">EA 23.325</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>

--- a/Mod_Korean/Lang/KR/Game/Block.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Block.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="579">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.325</t>
+    <t xml:space="preserve">EA 23.338 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
@@ -1335,6 +1335,24 @@
   </si>
   <si>
     <t xml:space="preserve">213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lattice wall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">格子の壁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 11.1</t>
@@ -1839,7 +1857,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -1851,10 +1869,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C4" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1870,10 +1888,10 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C5" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -1889,10 +1907,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C6" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -1908,10 +1926,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C7" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -1927,10 +1945,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C8" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
@@ -1946,10 +1964,10 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C9" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -1965,10 +1983,10 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C10" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -1984,10 +2002,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C11" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -2003,10 +2021,10 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C12" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
@@ -2022,10 +2040,10 @@
         <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C13" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
@@ -2041,10 +2059,10 @@
         <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C14" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
@@ -2060,10 +2078,10 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C15" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D15" t="s">
         <v>44</v>
@@ -2079,10 +2097,10 @@
         <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C16" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D16" t="s">
         <v>47</v>
@@ -2091,7 +2109,7 @@
         <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="G16"/>
       <c r="H16" t="s">
@@ -2103,10 +2121,10 @@
         <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C17" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D17" t="s">
         <v>44</v>
@@ -2122,10 +2140,10 @@
         <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C18" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="D18" t="s">
         <v>52</v>
@@ -2141,10 +2159,10 @@
         <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C19" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D19" t="s">
         <v>35</v>
@@ -2160,10 +2178,10 @@
         <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C20" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="D20" t="s">
         <v>56</v>
@@ -2179,10 +2197,10 @@
         <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C21" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="D21" t="s">
         <v>59</v>
@@ -2198,10 +2216,10 @@
         <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C22" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D22" t="s">
         <v>35</v>
@@ -2217,10 +2235,10 @@
         <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C23" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D23" t="s">
         <v>35</v>
@@ -2236,10 +2254,10 @@
         <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C24" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D24" t="s">
         <v>35</v>
@@ -2255,10 +2273,10 @@
         <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C25" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="D25" t="s">
         <v>65</v>
@@ -2274,10 +2292,10 @@
         <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C26" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="D26" t="s">
         <v>52</v>
@@ -2293,10 +2311,10 @@
         <v>68</v>
       </c>
       <c r="B27" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C27" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="D27" t="s">
         <v>69</v>
@@ -2312,10 +2330,10 @@
         <v>71</v>
       </c>
       <c r="B28" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C28" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="D28" t="s">
         <v>72</v>
@@ -2331,10 +2349,10 @@
         <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C29" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D29" t="s">
         <v>75</v>
@@ -2350,10 +2368,10 @@
         <v>77</v>
       </c>
       <c r="B30" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C30" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
@@ -2369,10 +2387,10 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C31" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D31" t="s">
         <v>47</v>
@@ -2381,7 +2399,7 @@
         <v>48</v>
       </c>
       <c r="F31" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="G31"/>
       <c r="H31" t="s">
@@ -2393,10 +2411,10 @@
         <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C32" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D32" t="s">
         <v>80</v>
@@ -2412,10 +2430,10 @@
         <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C33" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D33" t="s">
         <v>83</v>
@@ -2431,10 +2449,10 @@
         <v>85</v>
       </c>
       <c r="B34" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C34" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D34" t="s">
         <v>83</v>
@@ -2450,10 +2468,10 @@
         <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C35" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D35" t="s">
         <v>83</v>
@@ -2469,10 +2487,10 @@
         <v>87</v>
       </c>
       <c r="B36" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C36" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D36" t="s">
         <v>88</v>
@@ -2488,10 +2506,10 @@
         <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C37" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="D37" t="s">
         <v>91</v>
@@ -2507,10 +2525,10 @@
         <v>93</v>
       </c>
       <c r="B38" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C38" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="D38" t="s">
         <v>94</v>
@@ -2526,10 +2544,10 @@
         <v>96</v>
       </c>
       <c r="B39" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C39" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="D39" t="s">
         <v>97</v>
@@ -2545,10 +2563,10 @@
         <v>99</v>
       </c>
       <c r="B40" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C40" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="D40" t="s">
         <v>29</v>
@@ -2564,10 +2582,10 @@
         <v>100</v>
       </c>
       <c r="B41" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C41" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="D41" t="s">
         <v>29</v>
@@ -2583,10 +2601,10 @@
         <v>101</v>
       </c>
       <c r="B42" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C42" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="D42" t="s">
         <v>29</v>
@@ -2602,10 +2620,10 @@
         <v>102</v>
       </c>
       <c r="B43" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C43" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="D43" t="s">
         <v>29</v>
@@ -2621,10 +2639,10 @@
         <v>103</v>
       </c>
       <c r="B44" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C44" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="D44" t="s">
         <v>29</v>
@@ -2640,10 +2658,10 @@
         <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C45" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
@@ -2659,10 +2677,10 @@
         <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C46" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D46" t="s">
         <v>75</v>
@@ -2678,10 +2696,10 @@
         <v>106</v>
       </c>
       <c r="B47" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C47" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D47" t="s">
         <v>14</v>
@@ -2697,10 +2715,10 @@
         <v>107</v>
       </c>
       <c r="B48" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C48" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="D48" t="s">
         <v>108</v>
@@ -2716,10 +2734,10 @@
         <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C49" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="D49" t="s">
         <v>111</v>
@@ -2735,10 +2753,10 @@
         <v>113</v>
       </c>
       <c r="B50" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C50" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="D50" t="s">
         <v>114</v>
@@ -2754,10 +2772,10 @@
         <v>116</v>
       </c>
       <c r="B51" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C51" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="D51" t="s">
         <v>117</v>
@@ -2773,10 +2791,10 @@
         <v>119</v>
       </c>
       <c r="B52" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C52" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="D52" t="s">
         <v>120</v>
@@ -2792,10 +2810,10 @@
         <v>122</v>
       </c>
       <c r="B53" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C53" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="D53" t="s">
         <v>123</v>
@@ -2811,10 +2829,10 @@
         <v>125</v>
       </c>
       <c r="B54" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C54" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="D54" t="s">
         <v>126</v>
@@ -2830,10 +2848,10 @@
         <v>128</v>
       </c>
       <c r="B55" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C55" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D55" t="s">
         <v>129</v>
@@ -2849,10 +2867,10 @@
         <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C56" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D56" t="s">
         <v>132</v>
@@ -2868,10 +2886,10 @@
         <v>134</v>
       </c>
       <c r="B57" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C57" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="D57" t="s">
         <v>135</v>
@@ -2887,10 +2905,10 @@
         <v>137</v>
       </c>
       <c r="B58" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C58" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="D58" t="s">
         <v>117</v>
@@ -2906,10 +2924,10 @@
         <v>138</v>
       </c>
       <c r="B59" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C59" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D59" t="s">
         <v>139</v>
@@ -2925,10 +2943,10 @@
         <v>141</v>
       </c>
       <c r="B60" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C60" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D60" t="s">
         <v>142</v>
@@ -2944,10 +2962,10 @@
         <v>144</v>
       </c>
       <c r="B61" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C61" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D61" t="s">
         <v>142</v>
@@ -2963,10 +2981,10 @@
         <v>145</v>
       </c>
       <c r="B62" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C62" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D62" t="s">
         <v>142</v>
@@ -2982,10 +3000,10 @@
         <v>146</v>
       </c>
       <c r="B63" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C63" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="D63" t="s">
         <v>147</v>
@@ -3001,10 +3019,10 @@
         <v>149</v>
       </c>
       <c r="B64" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C64" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D64" t="s">
         <v>150</v>
@@ -3020,10 +3038,10 @@
         <v>152</v>
       </c>
       <c r="B65" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C65" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D65" t="s">
         <v>150</v>
@@ -3039,10 +3057,10 @@
         <v>153</v>
       </c>
       <c r="B66" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C66" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D66" t="s">
         <v>150</v>
@@ -3058,10 +3076,10 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C67" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="D67" t="s">
         <v>120</v>
@@ -3077,10 +3095,10 @@
         <v>155</v>
       </c>
       <c r="B68" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C68" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D68" t="s">
         <v>14</v>
@@ -3096,10 +3114,10 @@
         <v>156</v>
       </c>
       <c r="B69" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C69" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D69" t="s">
         <v>14</v>
@@ -3115,10 +3133,10 @@
         <v>157</v>
       </c>
       <c r="B70" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C70" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D70" t="s">
         <v>158</v>
@@ -3134,10 +3152,10 @@
         <v>160</v>
       </c>
       <c r="B71" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C71" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="D71" t="s">
         <v>161</v>
@@ -3153,10 +3171,10 @@
         <v>163</v>
       </c>
       <c r="B72" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C72" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D72" t="s">
         <v>158</v>
@@ -3172,10 +3190,10 @@
         <v>164</v>
       </c>
       <c r="B73" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C73" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="D73" t="s">
         <v>165</v>
@@ -3191,10 +3209,10 @@
         <v>167</v>
       </c>
       <c r="B74" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C74" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D74" t="s">
         <v>168</v>
@@ -3210,10 +3228,10 @@
         <v>170</v>
       </c>
       <c r="B75" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C75" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D75" t="s">
         <v>168</v>
@@ -3229,10 +3247,10 @@
         <v>171</v>
       </c>
       <c r="B76" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C76" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D76" t="s">
         <v>158</v>
@@ -3248,10 +3266,10 @@
         <v>172</v>
       </c>
       <c r="B77" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C77" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D77" t="s">
         <v>168</v>
@@ -3267,10 +3285,10 @@
         <v>173</v>
       </c>
       <c r="B78" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C78" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D78" t="s">
         <v>158</v>
@@ -3286,10 +3304,10 @@
         <v>174</v>
       </c>
       <c r="B79" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C79" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D79" t="s">
         <v>168</v>
@@ -3305,10 +3323,10 @@
         <v>175</v>
       </c>
       <c r="B80" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C80" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="D80" t="s">
         <v>176</v>
@@ -3324,10 +3342,10 @@
         <v>178</v>
       </c>
       <c r="B81" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C81" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="D81" t="s">
         <v>176</v>
@@ -3343,10 +3361,10 @@
         <v>179</v>
       </c>
       <c r="B82" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C82" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="D82" t="s">
         <v>176</v>
@@ -3362,10 +3380,10 @@
         <v>180</v>
       </c>
       <c r="B83" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C83" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D83" t="s">
         <v>158</v>
@@ -3381,10 +3399,10 @@
         <v>181</v>
       </c>
       <c r="B84" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C84" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D84" t="s">
         <v>168</v>
@@ -3400,10 +3418,10 @@
         <v>182</v>
       </c>
       <c r="B85" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C85" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D85" t="s">
         <v>168</v>
@@ -3419,10 +3437,10 @@
         <v>183</v>
       </c>
       <c r="B86" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C86" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="D86" t="s">
         <v>184</v>
@@ -3438,10 +3456,10 @@
         <v>186</v>
       </c>
       <c r="B87" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C87" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="D87" t="s">
         <v>187</v>
@@ -3457,10 +3475,10 @@
         <v>189</v>
       </c>
       <c r="B88" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C88" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="D88" t="s">
         <v>187</v>
@@ -3476,10 +3494,10 @@
         <v>190</v>
       </c>
       <c r="B89" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C89" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="D89" t="s">
         <v>187</v>
@@ -3495,10 +3513,10 @@
         <v>191</v>
       </c>
       <c r="B90" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C90" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="D90" t="s">
         <v>161</v>
@@ -3514,10 +3532,10 @@
         <v>192</v>
       </c>
       <c r="B91" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C91" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="D91" t="s">
         <v>193</v>
@@ -3533,10 +3551,10 @@
         <v>195</v>
       </c>
       <c r="B92" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C92" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="D92" t="s">
         <v>114</v>
@@ -3552,10 +3570,10 @@
         <v>196</v>
       </c>
       <c r="B93" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C93" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="D93" t="s">
         <v>114</v>
@@ -3571,10 +3589,10 @@
         <v>197</v>
       </c>
       <c r="B94" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C94" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="D94" t="s">
         <v>198</v>
@@ -3590,10 +3608,10 @@
         <v>200</v>
       </c>
       <c r="B95" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C95" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D95" t="s">
         <v>139</v>
@@ -3609,10 +3627,10 @@
         <v>201</v>
       </c>
       <c r="B96" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C96" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="D96" t="s">
         <v>202</v>
@@ -3628,10 +3646,10 @@
         <v>204</v>
       </c>
       <c r="B97" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C97" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="D97" t="s">
         <v>202</v>
@@ -3647,10 +3665,10 @@
         <v>205</v>
       </c>
       <c r="B98" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C98" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="D98" t="s">
         <v>206</v>
@@ -3666,10 +3684,10 @@
         <v>208</v>
       </c>
       <c r="B99" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C99" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="D99" t="s">
         <v>209</v>
@@ -3685,10 +3703,10 @@
         <v>211</v>
       </c>
       <c r="B100" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C100" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="D100" t="s">
         <v>212</v>
@@ -3704,10 +3722,10 @@
         <v>214</v>
       </c>
       <c r="B101" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C101" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D101" t="s">
         <v>215</v>
@@ -3723,10 +3741,10 @@
         <v>217</v>
       </c>
       <c r="B102" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C102" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="D102" t="s">
         <v>218</v>
@@ -3742,10 +3760,10 @@
         <v>220</v>
       </c>
       <c r="B103" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C103" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D103" t="s">
         <v>221</v>
@@ -3761,10 +3779,10 @@
         <v>223</v>
       </c>
       <c r="B104" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C104" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D104" t="s">
         <v>221</v>
@@ -3780,10 +3798,10 @@
         <v>224</v>
       </c>
       <c r="B105" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C105" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="D105" t="s">
         <v>225</v>
@@ -3799,10 +3817,10 @@
         <v>227</v>
       </c>
       <c r="B106" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C106" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="D106" t="s">
         <v>225</v>
@@ -3818,10 +3836,10 @@
         <v>228</v>
       </c>
       <c r="B107" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C107" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="D107" t="s">
         <v>225</v>
@@ -3837,10 +3855,10 @@
         <v>229</v>
       </c>
       <c r="B108" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C108" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="D108" t="s">
         <v>225</v>
@@ -3856,10 +3874,10 @@
         <v>230</v>
       </c>
       <c r="B109" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C109" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="D109" t="s">
         <v>20</v>
@@ -3875,10 +3893,10 @@
         <v>231</v>
       </c>
       <c r="B110" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C110" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="D110" t="s">
         <v>232</v>
@@ -3894,10 +3912,10 @@
         <v>234</v>
       </c>
       <c r="B111" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C111" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="D111" t="s">
         <v>235</v>
@@ -3913,10 +3931,10 @@
         <v>237</v>
       </c>
       <c r="B112" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C112" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="D112" t="s">
         <v>235</v>
@@ -3932,10 +3950,10 @@
         <v>238</v>
       </c>
       <c r="B113" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C113" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="D113" t="s">
         <v>235</v>
@@ -3951,10 +3969,10 @@
         <v>239</v>
       </c>
       <c r="B114" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C114" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="D114" t="s">
         <v>235</v>
@@ -3970,10 +3988,10 @@
         <v>240</v>
       </c>
       <c r="B115" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C115" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D115" t="s">
         <v>241</v>
@@ -3989,10 +4007,10 @@
         <v>243</v>
       </c>
       <c r="B116" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C116" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D116" t="s">
         <v>241</v>
@@ -4008,10 +4026,10 @@
         <v>244</v>
       </c>
       <c r="B117" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C117" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="D117" t="s">
         <v>245</v>
@@ -4027,10 +4045,10 @@
         <v>247</v>
       </c>
       <c r="B118" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C118" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="D118" t="s">
         <v>248</v>
@@ -4046,10 +4064,10 @@
         <v>250</v>
       </c>
       <c r="B119" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C119" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="D119" t="s">
         <v>248</v>
@@ -4065,10 +4083,10 @@
         <v>251</v>
       </c>
       <c r="B120" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C120" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="D120" t="s">
         <v>248</v>
@@ -4084,10 +4102,10 @@
         <v>252</v>
       </c>
       <c r="B121" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C121" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="D121" t="s">
         <v>253</v>
@@ -4103,10 +4121,10 @@
         <v>255</v>
       </c>
       <c r="B122" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C122" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="D122" t="s">
         <v>253</v>
@@ -4122,10 +4140,10 @@
         <v>256</v>
       </c>
       <c r="B123" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C123" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="D123" t="s">
         <v>257</v>
@@ -4141,10 +4159,10 @@
         <v>259</v>
       </c>
       <c r="B124" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C124" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="D124" t="s">
         <v>257</v>
@@ -4160,10 +4178,10 @@
         <v>260</v>
       </c>
       <c r="B125" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C125" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="D125" t="s">
         <v>257</v>
@@ -4179,10 +4197,10 @@
         <v>261</v>
       </c>
       <c r="B126" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C126" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="D126" t="s">
         <v>248</v>
@@ -4198,10 +4216,10 @@
         <v>262</v>
       </c>
       <c r="B127" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C127" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="D127" t="s">
         <v>263</v>
@@ -4217,10 +4235,10 @@
         <v>265</v>
       </c>
       <c r="B128" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C128" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D128" t="s">
         <v>158</v>
@@ -4236,10 +4254,10 @@
         <v>266</v>
       </c>
       <c r="B129" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C129" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="D129" t="s">
         <v>29</v>
@@ -4255,10 +4273,10 @@
         <v>267</v>
       </c>
       <c r="B130" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C130" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="D130" t="s">
         <v>120</v>
@@ -4274,10 +4292,10 @@
         <v>268</v>
       </c>
       <c r="B131" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C131" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="D131" t="s">
         <v>269</v>
@@ -4286,7 +4304,7 @@
         <v>270</v>
       </c>
       <c r="F131" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="G131" t="s">
         <v>271</v>
@@ -4300,10 +4318,10 @@
         <v>273</v>
       </c>
       <c r="B132" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C132" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D132" t="s">
         <v>35</v>
@@ -4319,10 +4337,10 @@
         <v>274</v>
       </c>
       <c r="B133" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C133" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="D133" t="s">
         <v>275</v>
@@ -4338,10 +4356,10 @@
         <v>277</v>
       </c>
       <c r="B134" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C134" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="D134" t="s">
         <v>278</v>
@@ -4357,10 +4375,10 @@
         <v>280</v>
       </c>
       <c r="B135" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C135" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D135" t="s">
         <v>281</v>
@@ -4376,10 +4394,10 @@
         <v>283</v>
       </c>
       <c r="B136" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C136" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="D136" t="s">
         <v>281</v>
@@ -4395,10 +4413,10 @@
         <v>285</v>
       </c>
       <c r="B137" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C137" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="D137" t="s">
         <v>281</v>
@@ -4414,10 +4432,10 @@
         <v>287</v>
       </c>
       <c r="B138" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C138" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D138" t="s">
         <v>221</v>
@@ -4433,10 +4451,10 @@
         <v>288</v>
       </c>
       <c r="B139" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C139" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="D139" t="s">
         <v>289</v>
@@ -4452,10 +4470,10 @@
         <v>291</v>
       </c>
       <c r="B140" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C140" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="D140" t="s">
         <v>120</v>
@@ -4471,10 +4489,10 @@
         <v>292</v>
       </c>
       <c r="B141" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C141" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="D141" t="s">
         <v>123</v>
@@ -4490,10 +4508,10 @@
         <v>293</v>
       </c>
       <c r="B142" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C142" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="D142" t="s">
         <v>117</v>
@@ -4509,10 +4527,10 @@
         <v>294</v>
       </c>
       <c r="B143" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C143" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D143" t="s">
         <v>35</v>
@@ -4528,10 +4546,10 @@
         <v>295</v>
       </c>
       <c r="B144" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C144" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="D144" t="s">
         <v>38</v>
@@ -4547,10 +4565,10 @@
         <v>296</v>
       </c>
       <c r="B145" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C145" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="D145" t="s">
         <v>117</v>
@@ -4566,10 +4584,10 @@
         <v>297</v>
       </c>
       <c r="B146" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C146" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D146" t="s">
         <v>35</v>
@@ -4585,10 +4603,10 @@
         <v>298</v>
       </c>
       <c r="B147" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C147" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="D147" t="s">
         <v>299</v>
@@ -4604,10 +4622,10 @@
         <v>301</v>
       </c>
       <c r="B148" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C148" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="D148" t="s">
         <v>302</v>
@@ -4623,10 +4641,10 @@
         <v>304</v>
       </c>
       <c r="B149" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C149" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="D149" t="s">
         <v>302</v>
@@ -4642,10 +4660,10 @@
         <v>305</v>
       </c>
       <c r="B150" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C150" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="D150" t="s">
         <v>306</v>
@@ -4661,10 +4679,10 @@
         <v>308</v>
       </c>
       <c r="B151" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C151" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D151" t="s">
         <v>150</v>
@@ -4680,10 +4698,10 @@
         <v>309</v>
       </c>
       <c r="B152" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C152" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="D152" t="s">
         <v>310</v>
@@ -4699,10 +4717,10 @@
         <v>312</v>
       </c>
       <c r="B153" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C153" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D153" t="s">
         <v>313</v>
@@ -4718,10 +4736,10 @@
         <v>315</v>
       </c>
       <c r="B154" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C154" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="D154" t="s">
         <v>316</v>
@@ -4737,10 +4755,10 @@
         <v>318</v>
       </c>
       <c r="B155" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C155" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="D155" t="s">
         <v>316</v>
@@ -4756,10 +4774,10 @@
         <v>319</v>
       </c>
       <c r="B156" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C156" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D156" t="s">
         <v>75</v>
@@ -4775,10 +4793,10 @@
         <v>320</v>
       </c>
       <c r="B157" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C157" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="D157" t="s">
         <v>111</v>
@@ -4794,10 +4812,10 @@
         <v>321</v>
       </c>
       <c r="B158" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C158" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D158" t="s">
         <v>221</v>
@@ -4813,10 +4831,10 @@
         <v>322</v>
       </c>
       <c r="B159" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C159" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D159" t="s">
         <v>150</v>
@@ -4832,10 +4850,10 @@
         <v>323</v>
       </c>
       <c r="B160" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C160" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D160" t="s">
         <v>150</v>
@@ -4851,10 +4869,10 @@
         <v>324</v>
       </c>
       <c r="B161" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="C161" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D161" t="s">
         <v>150</v>
@@ -4870,10 +4888,10 @@
         <v>325</v>
       </c>
       <c r="B162" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C162" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="D162" t="s">
         <v>108</v>
@@ -4889,10 +4907,10 @@
         <v>326</v>
       </c>
       <c r="B163" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C163" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="D163" t="s">
         <v>327</v>
@@ -4908,10 +4926,10 @@
         <v>329</v>
       </c>
       <c r="B164" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C164" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="D164" t="s">
         <v>289</v>
@@ -4927,10 +4945,10 @@
         <v>330</v>
       </c>
       <c r="B165" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C165" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D165" t="s">
         <v>331</v>
@@ -4946,10 +4964,10 @@
         <v>333</v>
       </c>
       <c r="B166" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C166" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="D166" t="s">
         <v>334</v>
@@ -4965,10 +4983,10 @@
         <v>336</v>
       </c>
       <c r="B167" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C167" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="D167" t="s">
         <v>334</v>
@@ -4984,10 +5002,10 @@
         <v>337</v>
       </c>
       <c r="B168" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C168" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="D168" t="s">
         <v>338</v>
@@ -5003,10 +5021,10 @@
         <v>340</v>
       </c>
       <c r="B169" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C169" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="D169" t="s">
         <v>341</v>
@@ -5022,10 +5040,10 @@
         <v>343</v>
       </c>
       <c r="B170" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C170" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="D170" t="s">
         <v>344</v>
@@ -5041,10 +5059,10 @@
         <v>346</v>
       </c>
       <c r="B171" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C171" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="D171" t="s">
         <v>347</v>
@@ -5060,10 +5078,10 @@
         <v>349</v>
       </c>
       <c r="B172" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="C172" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D172" t="s">
         <v>139</v>
@@ -5079,10 +5097,10 @@
         <v>350</v>
       </c>
       <c r="B173" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="C173" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D173" t="s">
         <v>139</v>
@@ -5098,10 +5116,10 @@
         <v>351</v>
       </c>
       <c r="B174" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C174" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="D174" t="s">
         <v>352</v>
@@ -5117,10 +5135,10 @@
         <v>354</v>
       </c>
       <c r="B175" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C175" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="D175" t="s">
         <v>355</v>
@@ -5136,10 +5154,10 @@
         <v>357</v>
       </c>
       <c r="B176" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C176" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="D176" t="s">
         <v>355</v>
@@ -5155,10 +5173,10 @@
         <v>358</v>
       </c>
       <c r="B177" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C177" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="D177" t="s">
         <v>359</v>
@@ -5174,10 +5192,10 @@
         <v>361</v>
       </c>
       <c r="B178" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="C178" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D178" t="s">
         <v>29</v>
@@ -5193,10 +5211,10 @@
         <v>362</v>
       </c>
       <c r="B179" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="C179" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D179" t="s">
         <v>29</v>
@@ -5212,10 +5230,10 @@
         <v>363</v>
       </c>
       <c r="B180" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C180" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D180" t="s">
         <v>29</v>
@@ -5231,10 +5249,10 @@
         <v>364</v>
       </c>
       <c r="B181" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C181" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D181" t="s">
         <v>29</v>
@@ -5250,10 +5268,10 @@
         <v>365</v>
       </c>
       <c r="B182" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C182" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D182" t="s">
         <v>29</v>
@@ -5269,10 +5287,10 @@
         <v>366</v>
       </c>
       <c r="B183" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C183" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D183" t="s">
         <v>29</v>
@@ -5288,10 +5306,10 @@
         <v>367</v>
       </c>
       <c r="B184" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C184" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D184" t="s">
         <v>29</v>
@@ -5307,10 +5325,10 @@
         <v>368</v>
       </c>
       <c r="B185" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C185" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D185" t="s">
         <v>29</v>
@@ -5326,10 +5344,10 @@
         <v>369</v>
       </c>
       <c r="B186" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C186" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D186" t="s">
         <v>29</v>
@@ -5345,10 +5363,10 @@
         <v>370</v>
       </c>
       <c r="B187" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C187" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D187" t="s">
         <v>29</v>
@@ -5364,10 +5382,10 @@
         <v>371</v>
       </c>
       <c r="B188" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C188" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D188" t="s">
         <v>14</v>
@@ -5383,10 +5401,10 @@
         <v>372</v>
       </c>
       <c r="B189" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C189" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="D189" t="s">
         <v>373</v>
@@ -5402,10 +5420,10 @@
         <v>375</v>
       </c>
       <c r="B190" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C190" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="D190" t="s">
         <v>376</v>
@@ -5421,10 +5439,10 @@
         <v>378</v>
       </c>
       <c r="B191" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C191" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="D191" t="s">
         <v>376</v>
@@ -5440,10 +5458,10 @@
         <v>379</v>
       </c>
       <c r="B192" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C192" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D192" t="s">
         <v>380</v>
@@ -5459,10 +5477,10 @@
         <v>382</v>
       </c>
       <c r="B193" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="C193" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="D193" t="s">
         <v>383</v>
@@ -5478,10 +5496,10 @@
         <v>385</v>
       </c>
       <c r="B194" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C194" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="D194" t="s">
         <v>386</v>
@@ -5497,10 +5515,10 @@
         <v>388</v>
       </c>
       <c r="B195" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C195" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="D195" t="s">
         <v>389</v>
@@ -5516,10 +5534,10 @@
         <v>391</v>
       </c>
       <c r="B196" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C196" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="D196" t="s">
         <v>392</v>
@@ -5535,10 +5553,10 @@
         <v>394</v>
       </c>
       <c r="B197" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C197" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="D197" t="s">
         <v>395</v>
@@ -5554,10 +5572,10 @@
         <v>397</v>
       </c>
       <c r="B198" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C198" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="D198" t="s">
         <v>398</v>
@@ -5573,10 +5591,10 @@
         <v>400</v>
       </c>
       <c r="B199" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C199" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="D199" t="s">
         <v>401</v>
@@ -5592,10 +5610,10 @@
         <v>403</v>
       </c>
       <c r="B200" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C200" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D200" t="s">
         <v>404</v>
@@ -5611,10 +5629,10 @@
         <v>406</v>
       </c>
       <c r="B201" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C201" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="D201" t="s">
         <v>407</v>
@@ -5630,10 +5648,10 @@
         <v>409</v>
       </c>
       <c r="B202" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C202" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="D202" t="s">
         <v>410</v>
@@ -5649,10 +5667,10 @@
         <v>412</v>
       </c>
       <c r="B203" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="C203" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="D203" t="s">
         <v>413</v>
@@ -5668,10 +5686,10 @@
         <v>415</v>
       </c>
       <c r="B204" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="C204" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="D204" t="s">
         <v>59</v>
@@ -5687,10 +5705,10 @@
         <v>416</v>
       </c>
       <c r="B205" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="C205" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D205" t="s">
         <v>417</v>
@@ -5706,10 +5724,10 @@
         <v>419</v>
       </c>
       <c r="B206" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="C206" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D206" t="s">
         <v>417</v>
@@ -5725,10 +5743,10 @@
         <v>420</v>
       </c>
       <c r="B207" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="C207" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="D207" t="s">
         <v>421</v>
@@ -5744,10 +5762,10 @@
         <v>423</v>
       </c>
       <c r="B208" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="C208" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D208" t="s">
         <v>424</v>
@@ -5763,10 +5781,10 @@
         <v>426</v>
       </c>
       <c r="B209" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="C209" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="D209" t="s">
         <v>427</v>
@@ -5782,10 +5800,10 @@
         <v>429</v>
       </c>
       <c r="B210" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C210" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="D210" t="s">
         <v>427</v>
@@ -5801,10 +5819,10 @@
         <v>430</v>
       </c>
       <c r="B211" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C211" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="D211" t="s">
         <v>431</v>
@@ -5820,10 +5838,10 @@
         <v>433</v>
       </c>
       <c r="B212" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C212" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="D212" t="s">
         <v>431</v>
@@ -5839,10 +5857,10 @@
         <v>434</v>
       </c>
       <c r="B213" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C213" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="D213" t="s">
         <v>431</v>
@@ -5858,10 +5876,10 @@
         <v>435</v>
       </c>
       <c r="B214" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C214" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D214" t="s">
         <v>436</v>
@@ -5877,10 +5895,10 @@
         <v>438</v>
       </c>
       <c r="B215" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C215" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D215" t="s">
         <v>436</v>
@@ -5896,10 +5914,10 @@
         <v>439</v>
       </c>
       <c r="B216" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C216" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D216" t="s">
         <v>436</v>
@@ -5909,6 +5927,70 @@
       </c>
       <c r="G216"/>
       <c r="H216"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>440</v>
+      </c>
+      <c r="B217" t="s">
+        <v>9</v>
+      </c>
+      <c r="D217" t="s">
+        <v>441</v>
+      </c>
+      <c r="E217" t="s">
+        <v>442</v>
+      </c>
+      <c r="G217"/>
+      <c r="H217"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>443</v>
+      </c>
+      <c r="B218" t="s">
+        <v>9</v>
+      </c>
+      <c r="D218" t="s">
+        <v>158</v>
+      </c>
+      <c r="E218" t="s">
+        <v>159</v>
+      </c>
+      <c r="G218"/>
+      <c r="H218"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>444</v>
+      </c>
+      <c r="B219" t="s">
+        <v>9</v>
+      </c>
+      <c r="D219" t="s">
+        <v>117</v>
+      </c>
+      <c r="E219" t="s">
+        <v>118</v>
+      </c>
+      <c r="G219"/>
+      <c r="H219"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>445</v>
+      </c>
+      <c r="B220" t="s">
+        <v>9</v>
+      </c>
+      <c r="D220" t="s">
+        <v>168</v>
+      </c>
+      <c r="E220" t="s">
+        <v>169</v>
+      </c>
+      <c r="G220"/>
+      <c r="H220"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>
